--- a/__test__/golden/xirr_golden_corpus.xlsx
+++ b/__test__/golden/xirr_golden_corpus.xlsx
@@ -186,7 +186,7 @@
     <t xml:space="preserve">nosolution/lease-tail</t>
   </si>
   <si>
-    <t xml:space="preserve">nosolution/all-tiny-outflow</t>
+    <t xml:space="preserve">edge/extreme-from-tiny-basis</t>
   </si>
   <si>
     <t xml:space="preserve">fuzz/000</t>
